--- a/apps/app-qt-print/docs/sample/サンプル_QuestionTime.xlsx
+++ b/apps/app-qt-print/docs/sample/サンプル_QuestionTime.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,95 +621,110 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Q1_和訳</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Q1_意図</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Q1_論点</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Q1_A例</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Q1_B例</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Q1_等価構造</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Q2_引用</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Q2_質問</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Q2_和訳</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>Q2_意図</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Q2_論点</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Q2_A例</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Q2_B例</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Q2_等価構造</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Q3_引用</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Q3_質問</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Q3_和訳</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
         <is>
           <t>Q3_意図</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Q3_論点</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Q3_A例</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Q3_B例</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Q3_等価構造</t>
         </is>
@@ -743,95 +758,110 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>あなたのessayには「若者はSNSを通じて面白い場所をすぐに共有する」とあります。ネット上の注目は数日で消えると言う人もいます。あなたならどう答えますか。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>SNSの注目は短命という反論を認めつつ理由を守れるか</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>SNSの注目はすぐ消えるという反論</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Although online attention can be short, each shared post can bring new visitors. Some of them may plan a trip and tell their friends.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Social media is very popular now. Many people use it every day.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Although ... / It is true that ..., but ... / Some people say ..., but ...</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>activities such as local food workshops help visitors meet residents</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Your essay says, “activities such as local food workshops help visitors meet residents.” If the town held the workshop online instead, would it work as well? Explain the difference.</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>あなたのessayには「地元の料理教室のような活動は、訪問者が住民と出会う助けになる」とあります。もし町がその教室をオンラインで開いたら、同じようにうまくいくでしょうか。違いを説明しなさい。</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>対面の交流という理由を別の形式に当てはめられるか</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>対面をオンラインに変えた場合の違い</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>If the workshop were online, more people could join, but visitors would not meet residents face to face, so they would understand the town less.</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Online events are convenient because people can join from home.</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>If ... would ... / Compared with ... / ... less ... than ...</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>creating programs for the young can build a long-term relationship with our town</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Your essay says, “creating programs for the young can build a long-term relationship with our town.” Say this again in two short and simple English sentences.</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>あなたのessayの「若者向けの企画を作ることで、町との長く続く関係を築ける」を、短く簡単な英文2文で言い直しなさい。</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>複雑な文を意味を保って平易に言い直せるか</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>「若者向けの企画」と「長く続く関係」</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>The town can make programs for young people. Then they may come back many times.</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>The town should make more programs for people.</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Two short sentences / Pronoun reference / because / so</t>
         </is>
@@ -865,95 +895,110 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>あなたのessayには「スマートフォンは、疑問があるときにすばやく情報を調べる助けになる」とあります。これでは生徒が自分で考えなくなると考える先生もいます。あなたならどう答えますか。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>自分で考えなくなるという反論に応答できるか</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>自分で考えなくなるという反論</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>It is true that students may stop thinking, but looking up facts quickly gives us more time to discuss our own ideas in class.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Many students like smartphones, and they are useful tools.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>It is true that ..., but ... / Although ... / Even if ...</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>learning how to use them responsibly at school is important</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Your essay says, “learning how to use them responsibly at school is important.” If a school allowed smartphones only during breaks, would students still learn this? Explain.</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>あなたのessayには「学校で責任ある使い方を学ぶことが大切だ」とあります。もし休み時間だけスマートフォンを許可する学校だったら、生徒はそれでも学べるでしょうか。説明しなさい。</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>責任ある使い方という理由を別条件に当てはめられるか</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>休み時間だけ許可した場合の違い</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>If phones were allowed only during breaks, students would learn less, because they would not practice using them for study with a teacher.</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Breaks are important for students to relax.</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>If ... would ... / less ... than ... / Compared with ...</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>many students already use digital tools at home</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Your essay says, “many students already use digital tools at school.” Say this sentence again in two short and simple sentences.</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>あなたのessayのこの文を、短く簡単な2文で言い直しなさい。</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>平易化</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>家でデジタル機器を使っていること</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Students use computers at home. They use phones too.</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>Digital tools are useful.</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Two short sentences / Pronoun reference / and</t>
         </is>
@@ -970,28 +1015,9 @@
           <t>【要確認】30語未満</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
